--- a/Stage/InstallatieInfo.xlsx
+++ b/Stage/InstallatieInfo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-3\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Desktop\LUCA-3\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F28B87-7693-43FF-9F04-3238643CC2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8DEDF1-AAB8-4F5D-9A52-23EEF0C381E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{407E7B6D-F412-4611-A616-D1C2B7E964EE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{407E7B6D-F412-4611-A616-D1C2B7E964EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -216,7 +216,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
@@ -555,9 +555,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6F76A2-70AC-4668-B644-993D6EB8C40C}">
   <dimension ref="B2:N33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
@@ -576,7 +576,7 @@
       </c>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -617,20 +617,20 @@
       </c>
       <c r="H4" s="2">
         <f>B4*$B$18</f>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K4" s="2">
         <f>MAX(0,H4-E4)</f>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -645,20 +645,20 @@
       </c>
       <c r="H5" s="2">
         <f t="shared" ref="H5:H15" si="0">B5*$B$18</f>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="K5" s="2">
         <f t="shared" ref="K5:K15" si="1">MAX(0,H5-E5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -673,20 +673,20 @@
       </c>
       <c r="H6" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K6" s="2">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B7" s="2">
         <v>1</v>
       </c>
@@ -701,20 +701,20 @@
       </c>
       <c r="H7" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="2">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B8" s="2">
         <v>1</v>
       </c>
@@ -729,20 +729,20 @@
       </c>
       <c r="H8" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="K8" s="2">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B9" s="2">
         <v>1</v>
       </c>
@@ -750,27 +750,27 @@
         <v>6</v>
       </c>
       <c r="E9" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="K9" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B10" s="2">
         <v>1</v>
       </c>
@@ -785,20 +785,20 @@
       </c>
       <c r="H10" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="K10" s="2">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B11" s="2">
         <v>1</v>
       </c>
@@ -813,20 +813,20 @@
       </c>
       <c r="H11" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K11" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B12" s="2">
         <v>1</v>
       </c>
@@ -841,20 +841,20 @@
       </c>
       <c r="H12" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K12" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B13" s="2">
         <v>3</v>
       </c>
@@ -869,20 +869,20 @@
       </c>
       <c r="H13" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K13" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B14" s="2">
         <v>3</v>
       </c>
@@ -897,20 +897,20 @@
       </c>
       <c r="H14" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K14" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B15" s="2">
         <v>1</v>
       </c>
@@ -925,30 +925,30 @@
       </c>
       <c r="H15" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="K15" s="2">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B17" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" s="6" t="s">
         <v>19</v>
       </c>
@@ -965,7 +965,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
@@ -984,7 +984,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="2" t="s">
         <v>1</v>
       </c>
@@ -1001,7 +1001,7 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
@@ -1020,7 +1020,7 @@
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B24" s="2" t="s">
         <v>3</v>
       </c>
@@ -1039,7 +1039,7 @@
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B25" s="2" t="s">
         <v>4</v>
       </c>
@@ -1058,7 +1058,7 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1077,7 +1077,7 @@
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B27" s="2" t="s">
         <v>6</v>
       </c>
@@ -1096,7 +1096,7 @@
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
@@ -1115,7 +1115,7 @@
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B29" s="2" t="s">
         <v>8</v>
       </c>
@@ -1134,7 +1134,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B30" s="2" t="s">
         <v>9</v>
       </c>
@@ -1153,7 +1153,7 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
@@ -1172,7 +1172,7 @@
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -1189,7 +1189,7 @@
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B33" s="2" t="s">
         <v>12</v>
       </c>

--- a/Stage/InstallatieInfo.xlsx
+++ b/Stage/InstallatieInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-3\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F28B87-7693-43FF-9F04-3238643CC2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CAEB4E-B2B6-4EF5-8B27-1317F74A57DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{407E7B6D-F412-4611-A616-D1C2B7E964EE}"/>
   </bookViews>
@@ -216,7 +216,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
@@ -555,9 +555,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6F76A2-70AC-4668-B644-993D6EB8C40C}">
   <dimension ref="B2:N33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:12" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
@@ -576,7 +576,7 @@
       </c>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -658,7 +658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -686,7 +686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>1</v>
       </c>
@@ -714,7 +714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>1</v>
       </c>
@@ -742,7 +742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>1</v>
       </c>
@@ -770,7 +770,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>1</v>
       </c>
@@ -798,7 +798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>1</v>
       </c>
@@ -826,7 +826,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>1</v>
       </c>
@@ -854,7 +854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
         <v>3</v>
       </c>
@@ -882,7 +882,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
         <v>3</v>
       </c>
@@ -910,7 +910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="2">
         <v>1</v>
       </c>
@@ -938,17 +938,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
         <v>19</v>
       </c>
@@ -965,7 +965,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
@@ -984,7 +984,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>1</v>
       </c>
@@ -1001,7 +1001,7 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
@@ -1020,7 +1020,7 @@
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>3</v>
       </c>
@@ -1039,7 +1039,7 @@
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>4</v>
       </c>
@@ -1058,7 +1058,7 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1077,7 +1077,7 @@
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>6</v>
       </c>
@@ -1096,7 +1096,7 @@
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
@@ -1115,7 +1115,7 @@
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>8</v>
       </c>
@@ -1134,7 +1134,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>9</v>
       </c>
@@ -1153,7 +1153,7 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
@@ -1172,7 +1172,7 @@
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -1189,7 +1189,7 @@
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
         <v>12</v>
       </c>
